--- a/load_and_merge_scripts/data/locks.xlsx
+++ b/load_and_merge_scripts/data/locks.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="Rf7a275fa08f14b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LockControl" sheetId="2" r:id="R4c8906c488684e3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LockColumnMap" sheetId="3" r:id="R0e2e771436864177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="Rc08818c3b8bf4061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LockControl" sheetId="2" r:id="R3bddf37e0aea41e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LockColumnMap" sheetId="3" r:id="R3200d187ff76421c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -842,16 +842,16 @@
         <x:v>model</x:v>
       </x:c>
       <x:c r="B3" s="64" t="str">
-        <x:v>model_scope</x:v>
+        <x:v>model_input_scope</x:v>
       </x:c>
       <x:c r="C3" s="64" t="str">
-        <x:v>model_scope_id</x:v>
+        <x:v>model_input_scope_id</x:v>
       </x:c>
       <x:c r="D3" s="64" t="str">
-        <x:v>model_scope_is_locked</x:v>
+        <x:v>model_input_scope_is_locked</x:v>
       </x:c>
       <x:c r="E3" s="65" t="str">
-        <x:v>Prefixed in current DDL.</x:v>
+        <x:v>Model Input Scope records only.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
